--- a/backtest_runs/20260410_193731/by_symbol/HUBC/HUBC.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/HUBC/HUBC.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-1372.160000000003</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>98627.84</v>
@@ -633,7 +633,7 @@
         <v>-5918.719999999987</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>100189.44</v>
@@ -679,7 +679,7 @@
         <v>-9318.400000000009</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>90871.03999999999</v>
@@ -771,7 +771,7 @@
         <v>-1244.160000000003</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>98842.87999999999</v>
@@ -817,7 +817,7 @@
         <v>-2616.319999999992</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>96226.56</v>
@@ -863,7 +863,7 @@
         <v>-824.320000000007</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>95402.23999999999</v>
@@ -909,7 +909,7 @@
         <v>-4915.199999999997</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>90487.03999999999</v>
@@ -1047,7 +1047,7 @@
         <v>-998.3999999999942</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>93968.64</v>
@@ -1185,7 +1185,7 @@
         <v>-3973.119999999995</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>95182.08</v>
@@ -1231,7 +1231,7 @@
         <v>-312.320000000007</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>94869.75999999999</v>
@@ -1277,7 +1277,7 @@
         <v>-1326.080000000002</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>93543.67999999999</v>
@@ -1415,7 +1415,7 @@
         <v>-3010.559999999998</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>94229.75999999999</v>
@@ -1461,7 +1461,7 @@
         <v>-245.7599999999948</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>93984</v>
@@ -1645,7 +1645,7 @@
         <v>-2513.919999999998</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>103430.4</v>
